--- a/artfynd/A 54810-2021 artfynd.xlsx
+++ b/artfynd/A 54810-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54810-2021 artfynd.xlsx
+++ b/artfynd/A 54810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97364907</v>
+        <v>97364908</v>
       </c>
       <c r="B2" t="n">
-        <v>73687</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>309</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Parknål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca hispidula</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527627.0195660596</v>
+        <v>527789</v>
       </c>
       <c r="R2" t="n">
-        <v>7030908.088189808</v>
+        <v>7030716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97364913</v>
+        <v>97364904</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527656.4007054815</v>
+        <v>527619</v>
       </c>
       <c r="R3" t="n">
-        <v>7030883.247714963</v>
+        <v>7030905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,34 +844,20 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Aälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97364915</v>
+        <v>97364911</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527621.1712371431</v>
+        <v>527623</v>
       </c>
       <c r="R4" t="n">
-        <v>7030909.830147265</v>
+        <v>7030909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +946,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,37 +979,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97364920</v>
+        <v>97364907</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Parknål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca hispidula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527690.8768313241</v>
+        <v>527627</v>
       </c>
       <c r="R5" t="n">
-        <v>7030840.078545813</v>
+        <v>7030908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,21 +1047,11 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,6 +1060,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,37 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97364916</v>
+        <v>97364915</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527622.6024195792</v>
+        <v>527622</v>
       </c>
       <c r="R6" t="n">
-        <v>7030951.964513418</v>
+        <v>7030910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1153,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97364904</v>
+        <v>97364920</v>
       </c>
       <c r="B7" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>306</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527618.0730029995</v>
+        <v>527691</v>
       </c>
       <c r="R7" t="n">
-        <v>7030904.874200743</v>
+        <v>7030840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,28 +1254,17 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97364911</v>
+        <v>97364903</v>
       </c>
       <c r="B8" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527622.9814322621</v>
+        <v>527622</v>
       </c>
       <c r="R8" t="n">
-        <v>7030908.053332782</v>
+        <v>7030910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,19 +1355,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,15 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97364918</v>
+        <v>97364905</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,21 +1399,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527629.7618832783</v>
+        <v>527667</v>
       </c>
       <c r="R9" t="n">
-        <v>7030954.266834565</v>
+        <v>7030873</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,19 +1456,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97364908</v>
+        <v>97364909</v>
       </c>
       <c r="B10" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,21 +1500,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527789.773102108</v>
+        <v>527688</v>
       </c>
       <c r="R10" t="n">
-        <v>7030716.356104937</v>
+        <v>7030847</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,19 +1557,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,12 +1593,7 @@
         <v>97364906</v>
       </c>
       <c r="B11" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527644.2436345569</v>
+        <v>527644</v>
       </c>
       <c r="R11" t="n">
-        <v>7030888.071922414</v>
+        <v>7030888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,19 +1658,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,15 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97364905</v>
+        <v>97364913</v>
       </c>
       <c r="B12" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527666.813427715</v>
+        <v>527656</v>
       </c>
       <c r="R12" t="n">
-        <v>7030872.58297848</v>
+        <v>7030884</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,21 +1759,11 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1942,6 +1772,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Aälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1962,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97364917</v>
+        <v>97364918</v>
       </c>
       <c r="B13" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527719.5867986089</v>
+        <v>527629</v>
       </c>
       <c r="R13" t="n">
-        <v>7030789.241059906</v>
+        <v>7030954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,19 +1865,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,15 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97364910</v>
+        <v>98822662</v>
       </c>
       <c r="B14" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,21 +1909,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2118,13 +1933,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527667.6953057682</v>
+        <v>527657</v>
       </c>
       <c r="R14" t="n">
-        <v>7030874.383061024</v>
+        <v>7030881</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,22 +1963,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,53 +1983,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97364909</v>
+        <v>97364916</v>
       </c>
       <c r="B15" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2234,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527688.1265357824</v>
+        <v>527623</v>
       </c>
       <c r="R15" t="n">
-        <v>7030846.776534377</v>
+        <v>7030952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2267,19 +2063,9 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,15 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97364903</v>
+        <v>98822661</v>
       </c>
       <c r="B16" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2326,21 +2107,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2350,13 +2131,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527621.1712371431</v>
+        <v>527609</v>
       </c>
       <c r="R16" t="n">
-        <v>7030909.830147265</v>
+        <v>7030911</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2380,22 +2161,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,31 +2181,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98822661</v>
+        <v>97364921</v>
       </c>
       <c r="B17" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,21 +2204,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2466,13 +2228,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527609.0491112004</v>
+        <v>527626</v>
       </c>
       <c r="R17" t="n">
-        <v>7030910.621765669</v>
+        <v>7030972</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2496,22 +2258,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,27 +2278,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98822662</v>
+        <v>97364910</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,21 +2305,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,13 +2329,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527657.3135647026</v>
+        <v>527668</v>
       </c>
       <c r="R18" t="n">
-        <v>7030881.463150141</v>
+        <v>7030875</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2608,22 +2359,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,15 +2379,120 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>97364917</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skyttmoberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>527720</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7030789</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54810-2021 artfynd.xlsx
+++ b/artfynd/A 54810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364904</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364911</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364907</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364915</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364920</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364903</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364905</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364909</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364906</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364918</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822662</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364916</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,6 +2265,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822661</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,6 +2371,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364921</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2392,6 +2477,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364910</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,8 +2583,33 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364917</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>